--- a/English/大雁单词.xlsx
+++ b/English/大雁单词.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\web\Englidh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E25385-6AA3-480D-8357-918D0DACCE86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13B7A60-1A63-4135-AC08-2D4DDD4BEF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Video 1" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,8 @@
     <sheet name="Video 23" sheetId="32" r:id="rId23"/>
     <sheet name="Video 24" sheetId="33" r:id="rId24"/>
     <sheet name="Video 25" sheetId="34" r:id="rId25"/>
-    <sheet name="Total 44" sheetId="13" r:id="rId26"/>
+    <sheet name="Video 26" sheetId="35" r:id="rId26"/>
+    <sheet name="Total 44" sheetId="13" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5111" uniqueCount="4164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5381" uniqueCount="4427">
   <si>
     <t>space</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -16715,6 +16716,1058 @@
   </si>
   <si>
     <t>n. 漏洞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cause</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 起因、理由、事业  v. 导致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>due</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 由于、预期的、应得的  n. 应付款</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 适当地、恰当地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>given</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 规定的、特定的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ingredient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 成分、材料、因素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>element</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 要素、因素、基础</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elementary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 基本的、初级的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>factor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 因素、要素</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 缘故</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 原谅、免除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>forgiving</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 宽宏大量的、宽容的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>curse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 诅咒、咒骂  n. 咒骂</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 责骂、训斥</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 控诉、控告、谴责</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accusation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 控告、谴责</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excuse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 原谅、免除  n. 借口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quarrel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 争吵、吵架</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>quarrelsome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 爱争吵的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 辱骂、侮辱、冒犯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consult</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 咨询、请教</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consultation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 咨询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consultative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 咨询的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consultant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 责备、责怪  n. 责备</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tame</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 驯服、制服  adj. 驯服的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>melt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 融化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 批评家、评论家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criticise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 批评</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criticism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 批评、批判</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>critical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 决定性的、关键的、严重的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>criterion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 标准、准则、原则</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 帮助、促进</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 帮助、援助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>assistant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 助手、助理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 抵挡、抵制、阻挡</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>resistance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 阻力、电阻、抵抗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 坚持、坚称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insistence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 坚持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insistent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 坚持的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 坚持、继续存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persistence</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>persistent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 坚持的、持续的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>consist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 由…组成、构成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>comprise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 包括、由…组成</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>praise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 表扬、赞美</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enterprise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 企业、规划、事业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>enterprising</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有事业心的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entrepreneur</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 企业家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>entrepreneurial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 创业的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corporation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 公司、法人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>corporate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 公司的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empire</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 帝国、大企业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>emperor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 皇帝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>empress</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 女皇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accompany</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 陪伴、伴随</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>companion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 同伴、朋友</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>companionship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 友情、友谊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 完成、解决、管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>management</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manager</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 管理人员、经理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>managerial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 经理的、管理的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chair</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 椅子、主席  v. 主持</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>chairman</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 主席、议长、会长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>president</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 总统、主席、董事长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presidency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 总统的职位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>presidential</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 总统的、国家主席的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>harness</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 控制、利用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>control</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 指挥、管理、控制</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 参加比赛</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competitor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 竞争对手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competitive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 竞争的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competition</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>competent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有能力的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>complete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 完成   adj. 完成的、彻底的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>completion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 完成、结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>versus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>对抗</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>crisis</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 危机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>finance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 资金、财政、金融</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>financial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 财政的、金融的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>funding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 专款、资金、提供资金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fund</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 基金、资金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commerce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 贸易、商业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commercial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 贸易的、赢利的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commercialise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 商业化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>commodity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 商品、有用的东西</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>goods</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 商品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>merchant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 商人、批发商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stock</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 库存、股票  v. 存货</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 贮藏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trade</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 贸易 v. 做生意</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trademark</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 商标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>budget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 预算</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>budgetary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 预算的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gadget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 小玩意、小装置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gadgetry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 小装置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 目标、靶子  v. 瞄准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>destination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 目的地、终点、目标</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revenue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 收入、收益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>avenue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 大街、途径、手段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>income</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gross</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 总的、毛的、严重的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>economy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 经济、国家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>economic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 经济学的、可赚钱的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>economics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 经济学、经济情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>economist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 经济学家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>economical</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 经济的、节俭的、节约的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scientific</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 科学上的、细致严谨的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>science</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 科学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scientist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 科学家</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>evil</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 恶毒的、邪恶的  n. 邪恶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>produce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 生产、制造、展现</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>product</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 产物、产品</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>production</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 生产、制造、制作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>productive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 生产的、有效益的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproduce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 复制、再生产</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproduction</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 生殖、繁衍</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reproductive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 繁殖的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>productivity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 生产率、生产力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industry</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 工业、行业、勤奋</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 工业的、产业的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrialize</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 工业化</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>industrious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 勤奋的、勤劳的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manipulate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 操作、操纵、影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manipulation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 控制、操纵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>manipulative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 善于控制的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 运作、工作、操作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 操作人员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 手术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>operational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 操作的、运转的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooperate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 合作、协作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooperation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 合作、协作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cooperative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 合作的、同心协力的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collaborate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collaboration</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collaborative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 合作的、协作的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -35367,6 +36420,1100 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EBE5E2-80D0-4BB8-A544-C7F5CF55B910}">
+  <dimension ref="A1:B135"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4164</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4166</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4168</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4170</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4172</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4174</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4175</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4176</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4178</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4179</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4180</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4181</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4182</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4183</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4184</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4185</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4186</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4188</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4190</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4191</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4192</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4193</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4194</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4197</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4200</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4201</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4202</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4203</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4204</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4205</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4206</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4207</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4209</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4211</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4213</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4214</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4215</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4216</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4217</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4219</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4220</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4221</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4223</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4224</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4225</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4227</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4229</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4231</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4233</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4234</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4235</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4236</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4237</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4239</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4241</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4243</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4238</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4245</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4246</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4249</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4250</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>4252</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4253</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4254</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4255</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4256</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4257</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4258</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4260</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4261</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4262</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>4264</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4265</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>4266</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4267</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>4268</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4269</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>4270</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4271</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>4272</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4273</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>4274</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4275</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>4276</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4277</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>4278</v>
+      </c>
+      <c r="B59" t="s">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>4279</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4280</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>4281</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4282</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>4283</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4284</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>4285</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4286</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>4287</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4288</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>4289</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4290</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>4291</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4292</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>4293</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4294</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>4295</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4296</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>4297</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4298</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>4299</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>4301</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4302</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>4303</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>4304</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4305</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>4306</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4307</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>4308</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4309</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>4310</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4311</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>4312</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>4314</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4315</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>4316</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4317</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>4318</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4319</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>4320</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4321</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>4322</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4323</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>4324</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4325</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>4326</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4327</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>4328</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4329</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>4330</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4331</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>4332</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4333</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>4334</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4335</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>4336</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4337</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>4338</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4339</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>4340</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4341</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>4342</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4343</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>4344</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4345</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>4346</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4347</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>4348</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4349</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>4350</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4351</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>4352</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4353</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>4354</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>4356</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4357</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>4358</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4355</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>4359</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4360</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>4361</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4362</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>4363</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4364</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>4365</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4366</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>4367</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4368</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>4369</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4370</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>4371</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4372</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>4373</v>
+      </c>
+      <c r="B108" t="s">
+        <v>4374</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>4375</v>
+      </c>
+      <c r="B109" t="s">
+        <v>4376</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>4377</v>
+      </c>
+      <c r="B110" t="s">
+        <v>4378</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>4379</v>
+      </c>
+      <c r="B111" t="s">
+        <v>4380</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>4381</v>
+      </c>
+      <c r="B112" t="s">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>4383</v>
+      </c>
+      <c r="B113" t="s">
+        <v>4384</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>4385</v>
+      </c>
+      <c r="B114" t="s">
+        <v>4386</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>4387</v>
+      </c>
+      <c r="B115" t="s">
+        <v>4388</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>4389</v>
+      </c>
+      <c r="B116" t="s">
+        <v>4390</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>4391</v>
+      </c>
+      <c r="B117" t="s">
+        <v>4392</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>4393</v>
+      </c>
+      <c r="B118" t="s">
+        <v>4394</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>4395</v>
+      </c>
+      <c r="B119" t="s">
+        <v>4396</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>4397</v>
+      </c>
+      <c r="B120" t="s">
+        <v>4398</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>4399</v>
+      </c>
+      <c r="B121" t="s">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>4401</v>
+      </c>
+      <c r="B122" t="s">
+        <v>4402</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>4403</v>
+      </c>
+      <c r="B123" t="s">
+        <v>4404</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>4405</v>
+      </c>
+      <c r="B124" t="s">
+        <v>4406</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>4407</v>
+      </c>
+      <c r="B125" t="s">
+        <v>4408</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>4409</v>
+      </c>
+      <c r="B126" t="s">
+        <v>4410</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>4411</v>
+      </c>
+      <c r="B127" t="s">
+        <v>4412</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>4413</v>
+      </c>
+      <c r="B128" t="s">
+        <v>4414</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>4415</v>
+      </c>
+      <c r="B129" t="s">
+        <v>4416</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>4417</v>
+      </c>
+      <c r="B130" t="s">
+        <v>4418</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>4419</v>
+      </c>
+      <c r="B131" t="s">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>4421</v>
+      </c>
+      <c r="B132" t="s">
+        <v>4422</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>4423</v>
+      </c>
+      <c r="B133" t="s">
+        <v>4418</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>4424</v>
+      </c>
+      <c r="B134" t="s">
+        <v>4420</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>4425</v>
+      </c>
+      <c r="B135" t="s">
+        <v>4426</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35902E0-5DA8-4F9A-A665-EE84FD306EF5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>

--- a/English/大雁单词.xlsx
+++ b/English/大雁单词.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13B7A60-1A63-4135-AC08-2D4DDD4BEF64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83B550D-82A7-4B71-A869-A0E35932B1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Video 1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,8 @@
     <sheet name="Video 24" sheetId="33" r:id="rId24"/>
     <sheet name="Video 25" sheetId="34" r:id="rId25"/>
     <sheet name="Video 26" sheetId="35" r:id="rId26"/>
-    <sheet name="Total 44" sheetId="13" r:id="rId27"/>
+    <sheet name="Video 27" sheetId="36" r:id="rId27"/>
+    <sheet name="Total 44" sheetId="13" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5381" uniqueCount="4427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5595" uniqueCount="4641">
   <si>
     <t>space</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -17768,6 +17769,862 @@
   </si>
   <si>
     <t>adj. 合作的、协作的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 利润、利益、好处  v. 得有益于..</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>profitable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有利可图的、有益的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>benefit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 利益、津贴 v. 使收益</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beneficial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有益的、有利的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>beneficiary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 受益者、受惠人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>salary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 薪水</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earnings</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 薪水、利润</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>earn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 挣得、博得、获得</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 工资  v. 开展、发动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 费用、酬金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 费用、票  v. 成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>farewell</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 告别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>welfare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 福利、救济、幸福</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pension</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 养老金、抚恤金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allowance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 津贴、补助</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>allow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 允许、准许、承认、给予</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 奖金、意外收获</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>award</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 授予 n. 奖品、奖金</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>raward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 报酬、赏金、回报  v. 奖励、奖赏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rewarding</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 值得做的、有益的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awkward</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 令人尴尬的、难对付的、笨拙的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 敬畏  v. 使敬畏</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 可怕的、极坏的、非常的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>awesome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 令人惊叹的、使人惊惧的、很好的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n.v 零售</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>retailer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 零售商</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tailor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 裁缝 v. 专门制作、定做</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detail</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 细节、详情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>detailed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 详细的、细致的、精细的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advertise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 为…做广告、宣传</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advertisement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 广告</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>advertising</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 广告活动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 酒吧、条、棒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barrier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 障碍物、阻力、分界线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>barrel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 桶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bucket</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 一桶、大量</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bargain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 便宜货、交易  v. 讨价还价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gain</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 获得、受益、增加  n. 增加、好处</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embarrass</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v.使窘迫、使尴尬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>embarrassment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 尴尬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 缺乏的、不足的、有缺点的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>deficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 缺乏、缺点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>artificial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 人工的、人造的、虚假的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 熟练的、精通的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>proficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 精通、熟练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>efficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 效率高的、能干的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>efficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 效率、效能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sufficient</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 充足的、足够的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>superficial</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 肤浅的、表面的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shallow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 浅滩  adj. 浅的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>shadow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 影子、阴影、影响</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lower</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 更低的、下面的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>low</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 低的、矮的、低级的、下层的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>swallow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 燕子  v. 吞下、咽下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hollow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 山谷、洼地  adj. 空的、空虚的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pillow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 枕头 v. 枕着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pillar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 支柱、柱子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>follow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 跟随、遵循</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>following</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 下述的、下列的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fellow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 人、家伙、伙伴  adj. 同事的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fellowship</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 友谊、交情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 间谍  v. 认出、查明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aspect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 方面、外貌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 纺纱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 怀疑  n. 嫌疑分子  adj. 可疑的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspicious</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 猜疑、怀疑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>suspicion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 可疑的、猜疑的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 调查、检查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 检查、视察</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>inspector</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 检察员、视察员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>check</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 检查、核对、制止  n. 支票、结账单</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cheque</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 支票</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examine</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 审查、测验</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examination</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 考试、审查</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examinee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 应试者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>examiner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 考官、审查人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>monitor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 显示屏、监视器、班长</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 尊重、重视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respectable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 体面的、值得尊敬的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respectful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有礼貌的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 分别的、各自的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>respectively</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 各自地、依次地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prospect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 前途、前景、预期、展望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prospective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有前途的、预期的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 推测、投机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 推测、投机买卖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>speculative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 猜测的、投机的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>perspective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 看法、观点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>standpoint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 立场、观点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>statement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 声明、观点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 观点、重点  v. 指、对着</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pointless</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 无意义的、无目标的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 观念、信念、理解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>notional</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 猜测的、理论上的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concept</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 观念、概念</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>conceptual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 观念上的、概念上的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telescope</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 望远镜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>telescopic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 望远镜的、放大的、伸缩的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 期待、预料、猜想</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expectation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 期望、希望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expectancy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 预期、期待、期望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anticipate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 预料、期望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>anticipation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 预期、预料</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 参加、参与</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 参与者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>participation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 参加</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>antique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 文物、古董  adj. 古老的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -37514,6 +38371,877 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98848FD4-CB05-4EEF-B530-7955D1D1F0FA}">
+  <dimension ref="A1:B107"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4427</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4428</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4429</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4430</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4431</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4433</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4434</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4435</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4436</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4437</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4438</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4439</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4440</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4441</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4442</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4443</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4444</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4445</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4447</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4448</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4449</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4450</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4451</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4452</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4453</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4454</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4455</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4457</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4458</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4459</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4460</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4461</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4463</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4465</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4466</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4467</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4468</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4469</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4470</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4471</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4473</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4474</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4475</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4476</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4477</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4478</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4479</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4480</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4481</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4482</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4483</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4484</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4485</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4486</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4487</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4488</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4489</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4490</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4491</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4492</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4493</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4494</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4495</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4496</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4497</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4498</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4499</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4501</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4502</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4503</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4504</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4505</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4506</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4507</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4508</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4509</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4510</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4511</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4512</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>4513</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4514</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4515</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4516</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>4517</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4518</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4520</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4522</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4524</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4525</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4526</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4527</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4528</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>4529</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>4531</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>4533</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>4535</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>4537</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4538</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>4539</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4540</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>4541</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4542</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>4543</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4544</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>4545</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4546</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>4547</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4548</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>4549</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4550</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>4551</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4552</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>4553</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4554</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>4555</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4556</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>4559</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4558</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>4557</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4560</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>4561</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4562</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>4563</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4564</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>4565</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4566</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>4567</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4568</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>4569</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>4571</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4572</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>4573</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4574</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>4575</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4576</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>4577</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4578</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>4579</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4580</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>4581</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4582</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>4583</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4584</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>4585</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4586</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>4587</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>4589</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4590</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>4591</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4592</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>4593</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4594</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>4595</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4596</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>4597</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4598</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>4599</v>
+      </c>
+      <c r="B87" t="s">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>4601</v>
+      </c>
+      <c r="B88" t="s">
+        <v>4602</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>4603</v>
+      </c>
+      <c r="B89" t="s">
+        <v>4604</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>4605</v>
+      </c>
+      <c r="B90" t="s">
+        <v>4606</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>4607</v>
+      </c>
+      <c r="B91" t="s">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>4609</v>
+      </c>
+      <c r="B92" t="s">
+        <v>4610</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>4611</v>
+      </c>
+      <c r="B93" t="s">
+        <v>4612</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>4613</v>
+      </c>
+      <c r="B94" t="s">
+        <v>4614</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>4615</v>
+      </c>
+      <c r="B95" t="s">
+        <v>4616</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>4617</v>
+      </c>
+      <c r="B96" t="s">
+        <v>4618</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>4619</v>
+      </c>
+      <c r="B97" t="s">
+        <v>4620</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>4621</v>
+      </c>
+      <c r="B98" t="s">
+        <v>4622</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>4623</v>
+      </c>
+      <c r="B99" t="s">
+        <v>4624</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>4625</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4626</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>4627</v>
+      </c>
+      <c r="B101" t="s">
+        <v>4628</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>4629</v>
+      </c>
+      <c r="B102" t="s">
+        <v>4630</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>4631</v>
+      </c>
+      <c r="B103" t="s">
+        <v>4632</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>4633</v>
+      </c>
+      <c r="B104" t="s">
+        <v>4634</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>4635</v>
+      </c>
+      <c r="B105" t="s">
+        <v>4636</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>4637</v>
+      </c>
+      <c r="B106" t="s">
+        <v>4638</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>4639</v>
+      </c>
+      <c r="B107" t="s">
+        <v>4640</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35902E0-5DA8-4F9A-A665-EE84FD306EF5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>

--- a/English/大雁单词.xlsx
+++ b/English/大雁单词.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83B550D-82A7-4B71-A869-A0E35932B1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F094BCF2-813E-4A04-B480-2C7D77F102AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="9" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="23" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Video 1" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,8 @@
     <sheet name="Video 25" sheetId="34" r:id="rId25"/>
     <sheet name="Video 26" sheetId="35" r:id="rId26"/>
     <sheet name="Video 27" sheetId="36" r:id="rId27"/>
-    <sheet name="Total 44" sheetId="13" r:id="rId28"/>
+    <sheet name="Video 28" sheetId="37" r:id="rId28"/>
+    <sheet name="Total 44" sheetId="13" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5595" uniqueCount="4641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5713" uniqueCount="4757">
   <si>
     <t>space</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -18625,6 +18626,470 @@
   </si>
   <si>
     <t>n. 文物、古董  adj. 古老的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>margin</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 边缘、利润、极限、白边</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>marginal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 小的、微不足道的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boundary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 边界、界限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bound</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 一定会、有义务  v. 跳跃</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bounce</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 跳动、弹起、反射  n. 弹跳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizon</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 地平线、范围、眼界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>horizontal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 地平线的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>edge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 刀口、边缘、优势</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hedge</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 树篱、防范措施</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>frontier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 边境、新领域</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>border</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 国界、边界  v. 与…接壤</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>import</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 进口</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>importation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>export</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 出口  v. 输出</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>exportation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>passport</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 护照、途径</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visa</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 签证</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specific</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 细节、详情  adj. 具体的、详细的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specifically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 特意、专门地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specify</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 具体说明</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specification</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 规格、说明书</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>especially</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 尤其、专门、非常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>particular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 特别的、挑剔的、详细的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>particularly</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 特别、尤其</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>special</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 特殊的、特设的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>specialist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doctor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 医生、博士  v. 篡改</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 专家、专科医生  adj. 专业的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doctorate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 博士学位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>doctoral</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 博士的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peculiar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 奇怪的、特殊的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>peculiarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 特点、奇怪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 唯一的、独特的、罕见的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>odd</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 奇怪的、临时的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oddity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 古怪、怪异</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>odds</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 可能性、概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>weird</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 奇异的、不寻常的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquaint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 使熟悉、使了解</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>acquaintance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 熟人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 熟悉的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>familiarity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 熟悉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>troublesome</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 引起麻烦、令人讨厌的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trouble</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 问题、困难、烦扰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bother</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 打扰 n. 麻烦、烦扰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>plague</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 困扰、使苦恼  n. 瘟疫、灾害</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>annoy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 使苦恼、使生气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>annoyance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 恼怒、生气</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignore</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 忽视、不予理睬</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignorance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 无知</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ignorant</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 无知的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neglect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n &amp; v. 忽略、忽视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>neglectful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 马虎的、不重视的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negative</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有害的、消极的、负面的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v.取消、使无效的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>negation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 反面、对立面、拒绝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>passive</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 被动的、消极的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 乐观主义的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>optimism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 乐观</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pessimistic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 悲观的、厌世的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pessimism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 悲观、悲观主义</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -39242,6 +39707,492 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8837B5A-76D8-4E67-BC60-8580F3823942}">
+  <dimension ref="A1:B59"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4641</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4643</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4644</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4645</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4646</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4647</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4648</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4649</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4651</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4653</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4654</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4655</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4657</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4659</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4660</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4661</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4662</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4663</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4665</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4664</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4666</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4668</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4667</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4669</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4670</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4671</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4672</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4673</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4674</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4675</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4676</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4677</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4678</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4679</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4680</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4681</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4682</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4683</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4684</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4685</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4686</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4687</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4688</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4689</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4692</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4690</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4691</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4693</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4694</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4695</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4696</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4697</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4698</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4699</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4701</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4702</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4703</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4704</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4705</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4706</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4707</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4708</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4709</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4710</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4711</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4712</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4713</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4714</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4715</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4716</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4717</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4718</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4719</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4720</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4721</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4722</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4723</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4724</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>4725</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4726</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4727</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4728</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>4729</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4730</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4731</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4732</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4733</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4734</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4735</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4736</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4737</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4738</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4739</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4740</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>4741</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4742</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>4743</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4744</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>4745</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4746</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>4747</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4748</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>4749</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4750</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>4751</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4752</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>4753</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4754</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>4755</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4756</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35902E0-5DA8-4F9A-A665-EE84FD306EF5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>

--- a/English/大雁单词.xlsx
+++ b/English/大雁单词.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F094BCF2-813E-4A04-B480-2C7D77F102AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AEC5E9-F9E8-4F29-BBEA-4D4ED2DA43A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15264" yWindow="0" windowWidth="15552" windowHeight="16656" firstSheet="23" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="25" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Video 1" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,8 @@
     <sheet name="Video 26" sheetId="35" r:id="rId26"/>
     <sheet name="Video 27" sheetId="36" r:id="rId27"/>
     <sheet name="Video 28" sheetId="37" r:id="rId28"/>
-    <sheet name="Total 44" sheetId="13" r:id="rId29"/>
+    <sheet name="Video 29" sheetId="38" r:id="rId29"/>
+    <sheet name="Total 44" sheetId="13" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5713" uniqueCount="4757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5885" uniqueCount="4928">
   <si>
     <t>space</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -19090,6 +19091,690 @@
   </si>
   <si>
     <t>n. 悲观、悲观主义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>opt</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 选择、挑选</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>option</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>compulsory</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 强制的、义务的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>course</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 课程、过程、航线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>case</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 实例、诉讼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>choice</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 选择、入选者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 选择、选拔  adj. 精选的、优等的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>selective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 选择性的、有选择的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lecture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 演讲、讲座、教训  v. 讲授、告诫、指责</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>lecturer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 讲课者、演讲者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 选举、推选、选择</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>election</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 选举、推选</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>elective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 选举的、可选择的、选修的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>poll</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 民意调查、投票</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 收集、收藏、采集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collection</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 收藏品、积聚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>collective</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 集体的、共有的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dialect</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>方言、土话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>accent</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 口音、腔调、重音</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>rhythm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 节奏、韵律</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tone</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 音调、语气、腔调</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tune</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 曲调、曲子、歌曲</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>orchestra</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 管弦乐队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outdoors</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 在户外、在野外  n. 旷野、郊外</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>outdoor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 户外的、室外的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>venture</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 企业、商业、冒险事业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adventure</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 冒险、奇遇</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adventurer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 冒险者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vacation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 假期  v. 度假、休假</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vocation</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 工作、职业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vocational</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 职业的、业务知识的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>excursion</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 远足、短途旅行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tour</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 旅行、观光</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tourism</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 旅游业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tourist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 旅游者、观光者</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>journey</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 旅行、历程</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cruise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 巡航、乘船游览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cruiser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 巡洋舰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>voyage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n &amp; v. 航行、旅行</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>yoga</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 瑜伽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>training</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 训练、培训、锻炼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>train</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 培训、训练</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trainee</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 实习生</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>trainer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 运动鞋、便鞋、教员</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>fit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 合身、适合 adj. 健康的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>well-being</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 健康、安乐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gym</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 体育馆、健身房</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>muscle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 肌肉、体力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>muscular</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 肌肉发达的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>calorie</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 卡路里</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 精力、活力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energetic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 精力充沛的、充满活力的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>energetically</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adv. 精力充沛地</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>battery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 电池</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vigorous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 精力充沛的、健壮的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dynamic</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 充满活力的、精力充沛的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dynamics</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 动力学</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 访问  n. 参观、逗留、看望</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 可见的、明显的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visibility</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 能见度、可见性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>invisible</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 看不见的、无形的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 修改、复习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>revision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 复习、温习</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>vision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 视力、视野、幻象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visionary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有眼力的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervise</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 监督、管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervision</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 监督、管理</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>supervisor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 监督人、主管人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 视力的、视觉的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>view</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 看法、风景  v. 看待</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gaze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n.&amp; v. 凝视、注视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glance</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 匆匆一看、一瞥、扫视</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>glimpse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 一瞥、一看  v. 瞥见</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>stare</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 凝视、盯着看</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scan</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 细看、扫描、审视  n. 浏览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scenner</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 扫描仪</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scandal</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 丑闻、流言蜚语、谣言</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scandalous</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 可耻的、不可原谅的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>browse</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v. 浏览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>browser</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 浏览器、浏览程序</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 视力、看见、视野</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sightseeing</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 观光、游览</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 洞察力、领悟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insightful</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>adj. 有深刻了解的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>oversight</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>n. 疏忽、忽略</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -40193,10 +40878,702 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35902E0-5DA8-4F9A-A665-EE84FD306EF5}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C5DD33-B8B7-446E-8652-826E854ECC53}">
+  <dimension ref="A1:B86"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4757</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4758</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4759</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4761</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4763</v>
+      </c>
+      <c r="B4" t="s">
+        <v>4764</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4765</v>
+      </c>
+      <c r="B5" t="s">
+        <v>4766</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4767</v>
+      </c>
+      <c r="B6" t="s">
+        <v>4768</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4769</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4770</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4771</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4760</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4772</v>
+      </c>
+      <c r="B9" t="s">
+        <v>4773</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4774</v>
+      </c>
+      <c r="B10" t="s">
+        <v>4775</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4776</v>
+      </c>
+      <c r="B11" t="s">
+        <v>4777</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4778</v>
+      </c>
+      <c r="B12" t="s">
+        <v>4779</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4780</v>
+      </c>
+      <c r="B13" t="s">
+        <v>4781</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4782</v>
+      </c>
+      <c r="B14" t="s">
+        <v>4783</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4784</v>
+      </c>
+      <c r="B15" t="s">
+        <v>4785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4786</v>
+      </c>
+      <c r="B16" t="s">
+        <v>4787</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4788</v>
+      </c>
+      <c r="B17" t="s">
+        <v>4789</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4790</v>
+      </c>
+      <c r="B18" t="s">
+        <v>4791</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4792</v>
+      </c>
+      <c r="B19" t="s">
+        <v>4793</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4794</v>
+      </c>
+      <c r="B20" t="s">
+        <v>4795</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4796</v>
+      </c>
+      <c r="B21" t="s">
+        <v>4797</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4798</v>
+      </c>
+      <c r="B22" t="s">
+        <v>4799</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4800</v>
+      </c>
+      <c r="B23" t="s">
+        <v>4801</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4802</v>
+      </c>
+      <c r="B24" t="s">
+        <v>4803</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4804</v>
+      </c>
+      <c r="B25" t="s">
+        <v>4805</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4806</v>
+      </c>
+      <c r="B26" t="s">
+        <v>4807</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4808</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4809</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4810</v>
+      </c>
+      <c r="B28" t="s">
+        <v>4811</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4812</v>
+      </c>
+      <c r="B29" t="s">
+        <v>4813</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4814</v>
+      </c>
+      <c r="B30" t="s">
+        <v>4815</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4816</v>
+      </c>
+      <c r="B31" t="s">
+        <v>4817</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4818</v>
+      </c>
+      <c r="B32" t="s">
+        <v>4819</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4820</v>
+      </c>
+      <c r="B33" t="s">
+        <v>4821</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4822</v>
+      </c>
+      <c r="B34" t="s">
+        <v>4823</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4824</v>
+      </c>
+      <c r="B35" t="s">
+        <v>4825</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4826</v>
+      </c>
+      <c r="B36" t="s">
+        <v>4827</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4828</v>
+      </c>
+      <c r="B37" t="s">
+        <v>4829</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4830</v>
+      </c>
+      <c r="B38" t="s">
+        <v>4831</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4832</v>
+      </c>
+      <c r="B39" t="s">
+        <v>4833</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4834</v>
+      </c>
+      <c r="B40" t="s">
+        <v>4835</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4836</v>
+      </c>
+      <c r="B41" t="s">
+        <v>4837</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4838</v>
+      </c>
+      <c r="B42" t="s">
+        <v>4839</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4840</v>
+      </c>
+      <c r="B43" t="s">
+        <v>4841</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>4842</v>
+      </c>
+      <c r="B44" t="s">
+        <v>4843</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4844</v>
+      </c>
+      <c r="B45" t="s">
+        <v>4845</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>4846</v>
+      </c>
+      <c r="B46" t="s">
+        <v>4847</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4848</v>
+      </c>
+      <c r="B47" t="s">
+        <v>4849</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4850</v>
+      </c>
+      <c r="B48" t="s">
+        <v>4851</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4852</v>
+      </c>
+      <c r="B49" t="s">
+        <v>4853</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4854</v>
+      </c>
+      <c r="B50" t="s">
+        <v>4855</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>4856</v>
+      </c>
+      <c r="B51" t="s">
+        <v>4857</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>4858</v>
+      </c>
+      <c r="B52" t="s">
+        <v>4859</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>4860</v>
+      </c>
+      <c r="B53" t="s">
+        <v>4861</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>4862</v>
+      </c>
+      <c r="B54" t="s">
+        <v>4863</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>4864</v>
+      </c>
+      <c r="B55" t="s">
+        <v>4865</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>4866</v>
+      </c>
+      <c r="B56" t="s">
+        <v>4867</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>4868</v>
+      </c>
+      <c r="B57" t="s">
+        <v>4869</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>4870</v>
+      </c>
+      <c r="B58" t="s">
+        <v>4871</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>4872</v>
+      </c>
+      <c r="B59" t="s">
+        <v>4873</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>4874</v>
+      </c>
+      <c r="B60" t="s">
+        <v>4875</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>4876</v>
+      </c>
+      <c r="B61" t="s">
+        <v>4877</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>4878</v>
+      </c>
+      <c r="B62" t="s">
+        <v>4879</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>4880</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4881</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>4882</v>
+      </c>
+      <c r="B64" t="s">
+        <v>4883</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>4884</v>
+      </c>
+      <c r="B65" t="s">
+        <v>4885</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>4886</v>
+      </c>
+      <c r="B66" t="s">
+        <v>4887</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>4888</v>
+      </c>
+      <c r="B67" t="s">
+        <v>4889</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>4890</v>
+      </c>
+      <c r="B68" t="s">
+        <v>4891</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>4892</v>
+      </c>
+      <c r="B69" t="s">
+        <v>4893</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>4894</v>
+      </c>
+      <c r="B70" t="s">
+        <v>4895</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>4896</v>
+      </c>
+      <c r="B71" t="s">
+        <v>4897</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>4898</v>
+      </c>
+      <c r="B72" t="s">
+        <v>4899</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>4900</v>
+      </c>
+      <c r="B73" t="s">
+        <v>4901</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>4902</v>
+      </c>
+      <c r="B74" t="s">
+        <v>4903</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>4904</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4905</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>4906</v>
+      </c>
+      <c r="B76" t="s">
+        <v>4907</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>4908</v>
+      </c>
+      <c r="B77" t="s">
+        <v>4909</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>4910</v>
+      </c>
+      <c r="B78" t="s">
+        <v>4911</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>4912</v>
+      </c>
+      <c r="B79" t="s">
+        <v>4913</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>4914</v>
+      </c>
+      <c r="B80" t="s">
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>4916</v>
+      </c>
+      <c r="B81" t="s">
+        <v>4917</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>4918</v>
+      </c>
+      <c r="B82" t="s">
+        <v>4919</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>4920</v>
+      </c>
+      <c r="B83" t="s">
+        <v>4921</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>4922</v>
+      </c>
+      <c r="B84" t="s">
+        <v>4923</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>4924</v>
+      </c>
+      <c r="B85" t="s">
+        <v>4925</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>4926</v>
+      </c>
+      <c r="B86" t="s">
+        <v>4927</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -40828,6 +42205,16 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35902E0-5DA8-4F9A-A665-EE84FD306EF5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/English/大雁单词.xlsx
+++ b/English/大雁单词.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\study\Study\English\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Reading\Study\Study\English\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9AEC5E9-F9E8-4F29-BBEA-4D4ED2DA43A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C27A97F0-8B00-4DD5-B2E3-15B95CB8E694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="25" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Video 1" sheetId="2" r:id="rId1"/>
@@ -56,8 +56,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -19782,20 +19780,27 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -19885,7 +19890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -19894,9 +19899,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -20180,21 +20186,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77EB334D-CD51-4B4D-886F-D4C199C5F610}">
   <dimension ref="A1:D97"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.5546875" customWidth="1"/>
-    <col min="2" max="2" width="39.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>83</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="D1">
@@ -20202,14 +20208,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>84</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D2">
@@ -20217,14 +20223,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>85</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D3">
@@ -20232,14 +20238,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="D4">
@@ -20247,14 +20253,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>87</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="8" t="s">
         <v>3</v>
       </c>
       <c r="D5">
@@ -20262,14 +20268,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>88</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="8" t="s">
         <v>4</v>
       </c>
       <c r="D6">
@@ -20277,14 +20283,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>79</v>
       </c>
       <c r="B7" t="s">
         <v>89</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="8" t="s">
         <v>79</v>
       </c>
       <c r="D7">
@@ -20292,14 +20298,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>90</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D8">
@@ -20307,14 +20313,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>80</v>
       </c>
       <c r="B9" t="s">
         <v>91</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="8" t="s">
         <v>80</v>
       </c>
       <c r="D9">
@@ -20322,14 +20328,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>6</v>
       </c>
       <c r="B10" t="s">
         <v>92</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D10">
@@ -20337,14 +20343,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="8" t="s">
         <v>7</v>
       </c>
       <c r="D11">
@@ -20352,14 +20358,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>74</v>
       </c>
       <c r="B12" t="s">
         <v>94</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="8" t="s">
         <v>74</v>
       </c>
       <c r="D12">
@@ -20367,14 +20373,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>75</v>
       </c>
       <c r="B13" t="s">
         <v>95</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="8" t="s">
         <v>75</v>
       </c>
       <c r="D13">
@@ -20382,14 +20388,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>8</v>
       </c>
       <c r="B14" t="s">
         <v>82</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D14">
@@ -20397,14 +20403,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>76</v>
       </c>
       <c r="B15" t="s">
         <v>81</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="8" t="s">
         <v>76</v>
       </c>
       <c r="D15">
@@ -20412,14 +20418,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>96</v>
       </c>
       <c r="B16" t="s">
         <v>97</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="8" t="s">
         <v>96</v>
       </c>
       <c r="D16">
@@ -20427,14 +20433,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>9</v>
       </c>
       <c r="B17" t="s">
         <v>98</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D17">
@@ -20442,14 +20448,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>77</v>
       </c>
       <c r="B18" t="s">
         <v>99</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="8" t="s">
         <v>77</v>
       </c>
       <c r="D18">
@@ -20457,14 +20463,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>78</v>
       </c>
       <c r="B19" t="s">
         <v>100</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="8" t="s">
         <v>78</v>
       </c>
       <c r="D19">
@@ -20472,14 +20478,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>10</v>
       </c>
       <c r="B20" t="s">
         <v>101</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="8" t="s">
         <v>10</v>
       </c>
       <c r="D20">
@@ -20487,14 +20493,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>11</v>
       </c>
       <c r="B21" t="s">
         <v>102</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="8" t="s">
         <v>11</v>
       </c>
       <c r="D21">
@@ -20502,14 +20508,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
       <c r="B22" t="s">
         <v>103</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="8" t="s">
         <v>12</v>
       </c>
       <c r="D22">
@@ -20517,14 +20523,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>13</v>
       </c>
       <c r="B23" t="s">
         <v>104</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="8" t="s">
         <v>13</v>
       </c>
       <c r="D23">
@@ -20532,14 +20538,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
       <c r="B24" t="s">
         <v>105</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D24">
@@ -20547,14 +20553,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>15</v>
       </c>
       <c r="B25" t="s">
         <v>106</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D25">
@@ -20562,14 +20568,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>16</v>
       </c>
       <c r="B26" t="s">
         <v>107</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="8" t="s">
         <v>16</v>
       </c>
       <c r="D26">
@@ -20577,14 +20583,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>17</v>
       </c>
       <c r="B27" t="s">
         <v>108</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="8" t="s">
         <v>17</v>
       </c>
       <c r="D27">
@@ -20592,14 +20598,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
       <c r="B28" t="s">
         <v>109</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="8" t="s">
         <v>18</v>
       </c>
       <c r="D28">
@@ -20607,14 +20613,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>19</v>
       </c>
       <c r="B29" t="s">
         <v>110</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="8" t="s">
         <v>19</v>
       </c>
       <c r="D29">
@@ -20622,14 +20628,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>20</v>
       </c>
       <c r="B30" t="s">
         <v>111</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D30">
@@ -20637,14 +20643,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>21</v>
       </c>
       <c r="B31" t="s">
         <v>112</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D31">
@@ -20652,14 +20658,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>23</v>
       </c>
       <c r="B32" t="s">
         <v>115</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="8" t="s">
         <v>23</v>
       </c>
       <c r="D32">
@@ -20667,14 +20673,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>22</v>
       </c>
       <c r="B33" t="s">
         <v>113</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="8" t="s">
         <v>22</v>
       </c>
       <c r="D33">
@@ -20682,14 +20688,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>114</v>
       </c>
       <c r="B34" t="s">
         <v>116</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C34" s="8" t="s">
         <v>114</v>
       </c>
       <c r="D34">
@@ -20697,14 +20703,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>24</v>
       </c>
       <c r="B35" t="s">
         <v>117</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C35" s="8" t="s">
         <v>24</v>
       </c>
       <c r="D35">
@@ -20712,14 +20718,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>25</v>
       </c>
       <c r="B36" t="s">
         <v>118</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C36" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D36">
@@ -20727,14 +20733,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>119</v>
       </c>
       <c r="B37" t="s">
         <v>120</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C37" s="8" t="s">
         <v>119</v>
       </c>
       <c r="D37">
@@ -20742,14 +20748,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>26</v>
       </c>
       <c r="B38" t="s">
         <v>121</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C38" s="8" t="s">
         <v>26</v>
       </c>
       <c r="D38">
@@ -20757,14 +20763,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>27</v>
       </c>
       <c r="B39" t="s">
         <v>122</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C39" s="8" t="s">
         <v>27</v>
       </c>
       <c r="D39">
@@ -20772,14 +20778,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>123</v>
       </c>
       <c r="B40" t="s">
         <v>126</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="8" t="s">
         <v>123</v>
       </c>
       <c r="D40">
@@ -20787,14 +20793,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>28</v>
       </c>
       <c r="B41" t="s">
         <v>127</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C41" s="8" t="s">
         <v>28</v>
       </c>
       <c r="D41">
@@ -20802,14 +20808,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>124</v>
       </c>
       <c r="B42" t="s">
         <v>128</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C42" s="8" t="s">
         <v>124</v>
       </c>
       <c r="D42">
@@ -20817,14 +20823,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>125</v>
       </c>
       <c r="B43" t="s">
         <v>129</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C43" s="8" t="s">
         <v>125</v>
       </c>
       <c r="D43">
@@ -20832,14 +20838,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>29</v>
       </c>
       <c r="B44" t="s">
         <v>130</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="8" t="s">
         <v>29</v>
       </c>
       <c r="D44">
@@ -20847,14 +20853,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>131</v>
       </c>
       <c r="B45" t="s">
         <v>132</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C45" s="8" t="s">
         <v>131</v>
       </c>
       <c r="D45">
@@ -20862,14 +20868,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>30</v>
       </c>
       <c r="B46" t="s">
         <v>133</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D46">
@@ -20877,14 +20883,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>31</v>
       </c>
       <c r="B47" t="s">
         <v>134</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="8" t="s">
         <v>31</v>
       </c>
       <c r="D47">
@@ -20892,14 +20898,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>32</v>
       </c>
       <c r="B48" t="s">
         <v>135</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="8" t="s">
         <v>32</v>
       </c>
       <c r="D48">
@@ -20907,14 +20913,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
       <c r="B49" t="s">
         <v>34</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C49" s="8" t="s">
         <v>33</v>
       </c>
       <c r="D49">
@@ -20922,14 +20928,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>35</v>
       </c>
       <c r="B50" t="s">
         <v>136</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D50">
@@ -20937,14 +20943,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>37</v>
       </c>
       <c r="B51" t="s">
         <v>137</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="8" t="s">
         <v>37</v>
       </c>
       <c r="D51">
@@ -20952,14 +20958,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>36</v>
       </c>
       <c r="B52" t="s">
         <v>138</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C52" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D52">
@@ -20967,14 +20973,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>139</v>
       </c>
       <c r="B53" t="s">
         <v>140</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="8" t="s">
         <v>139</v>
       </c>
       <c r="D53">
@@ -20982,14 +20988,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>38</v>
       </c>
       <c r="B54" t="s">
         <v>141</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C54" s="8" t="s">
         <v>38</v>
       </c>
       <c r="D54">
@@ -20997,14 +21003,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>142</v>
       </c>
       <c r="B55" t="s">
         <v>143</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C55" s="8" t="s">
         <v>142</v>
       </c>
       <c r="D55">
@@ -21012,14 +21018,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>39</v>
       </c>
       <c r="B56" t="s">
         <v>144</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C56" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D56">
@@ -21027,14 +21033,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>69</v>
       </c>
       <c r="B57" t="s">
         <v>145</v>
       </c>
-      <c r="C57" t="s">
+      <c r="C57" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D57">
@@ -21042,14 +21048,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>40</v>
       </c>
       <c r="B58" t="s">
         <v>146</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D58">
@@ -21057,14 +21063,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>41</v>
       </c>
       <c r="B59" t="s">
         <v>147</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="8" t="s">
         <v>41</v>
       </c>
       <c r="D59">
@@ -21072,14 +21078,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>42</v>
       </c>
       <c r="B60" t="s">
         <v>148</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="8" t="s">
         <v>42</v>
       </c>
       <c r="D60">
@@ -21087,14 +21093,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>43</v>
       </c>
       <c r="B61" t="s">
         <v>149</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="8" t="s">
         <v>43</v>
       </c>
       <c r="D61">
@@ -21102,14 +21108,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>44</v>
       </c>
       <c r="B62" t="s">
         <v>150</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C62" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D62">
@@ -21117,14 +21123,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>45</v>
       </c>
       <c r="B63" t="s">
         <v>151</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C63" s="8" t="s">
         <v>45</v>
       </c>
       <c r="D63">
@@ -21132,14 +21138,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>46</v>
       </c>
       <c r="B64" t="s">
         <v>152</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C64" s="8" t="s">
         <v>46</v>
       </c>
       <c r="D64">
@@ -21147,14 +21153,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>47</v>
       </c>
       <c r="B65" t="s">
         <v>153</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C65" s="8" t="s">
         <v>47</v>
       </c>
       <c r="D65">
@@ -21162,14 +21168,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>48</v>
       </c>
       <c r="B66" t="s">
         <v>154</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C66" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D66">
@@ -21177,14 +21183,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>49</v>
       </c>
       <c r="B67" t="s">
         <v>155</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C67" s="8" t="s">
         <v>49</v>
       </c>
       <c r="D67">
@@ -21192,14 +21198,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>50</v>
       </c>
       <c r="B68" t="s">
         <v>156</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C68" s="8" t="s">
         <v>50</v>
       </c>
       <c r="D68">
@@ -21207,14 +21213,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>51</v>
       </c>
       <c r="B69" t="s">
         <v>157</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C69" s="8" t="s">
         <v>51</v>
       </c>
       <c r="D69">
@@ -21222,14 +21228,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>52</v>
       </c>
       <c r="B70" t="s">
         <v>158</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C70" s="8" t="s">
         <v>52</v>
       </c>
       <c r="D70">
@@ -21237,14 +21243,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>53</v>
       </c>
       <c r="B71" t="s">
         <v>159</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C71" s="8" t="s">
         <v>53</v>
       </c>
       <c r="D71">
@@ -21252,14 +21258,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>160</v>
       </c>
       <c r="B72" t="s">
         <v>161</v>
       </c>
-      <c r="C72" t="s">
+      <c r="C72" s="8" t="s">
         <v>160</v>
       </c>
       <c r="D72">
@@ -21267,14 +21273,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>54</v>
       </c>
       <c r="B73" t="s">
         <v>162</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D73">
@@ -21282,14 +21288,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>55</v>
       </c>
       <c r="B74" t="s">
         <v>163</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="8" t="s">
         <v>55</v>
       </c>
       <c r="D74">
@@ -21297,14 +21303,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>164</v>
       </c>
       <c r="B75" t="s">
         <v>165</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="8" t="s">
         <v>164</v>
       </c>
       <c r="D75">
@@ -21312,14 +21318,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>166</v>
       </c>
       <c r="B76" t="s">
         <v>167</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="8" t="s">
         <v>166</v>
       </c>
       <c r="D76">
@@ -21327,14 +21333,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>56</v>
       </c>
       <c r="B77" t="s">
         <v>169</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="8" t="s">
         <v>56</v>
       </c>
       <c r="D77">
@@ -21342,14 +21348,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>57</v>
       </c>
       <c r="B78" t="s">
         <v>168</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C78" s="8" t="s">
         <v>57</v>
       </c>
       <c r="D78">
@@ -21357,14 +21363,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>170</v>
       </c>
       <c r="B79" t="s">
         <v>171</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C79" s="8" t="s">
         <v>170</v>
       </c>
       <c r="D79">
@@ -21372,14 +21378,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>58</v>
       </c>
       <c r="B80" t="s">
         <v>168</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C80" s="8" t="s">
         <v>58</v>
       </c>
       <c r="D80">
@@ -21387,14 +21393,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>59</v>
       </c>
       <c r="B81" t="s">
         <v>172</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C81" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D81">
@@ -21402,14 +21408,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>60</v>
       </c>
       <c r="B82" t="s">
         <v>173</v>
       </c>
-      <c r="C82" t="s">
+      <c r="C82" s="8" t="s">
         <v>60</v>
       </c>
       <c r="D82">
@@ -21417,14 +21423,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>174</v>
       </c>
       <c r="B83" t="s">
         <v>175</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C83" s="8" t="s">
         <v>174</v>
       </c>
       <c r="D83">
@@ -21432,14 +21438,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>61</v>
       </c>
       <c r="B84" t="s">
         <v>176</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C84" s="8" t="s">
         <v>61</v>
       </c>
       <c r="D84">
@@ -21447,14 +21453,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>62</v>
       </c>
       <c r="B85" t="s">
         <v>177</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C85" s="8" t="s">
         <v>62</v>
       </c>
       <c r="D85">
@@ -21462,14 +21468,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>63</v>
       </c>
       <c r="B86" t="s">
         <v>178</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C86" s="8" t="s">
         <v>63</v>
       </c>
       <c r="D86">
@@ -21477,14 +21483,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>70</v>
       </c>
       <c r="B87" t="s">
         <v>179</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C87" s="8" t="s">
         <v>70</v>
       </c>
       <c r="D87">
@@ -21492,14 +21498,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>180</v>
       </c>
       <c r="B88" t="s">
         <v>181</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C88" s="8" t="s">
         <v>180</v>
       </c>
       <c r="D88">
@@ -21507,14 +21513,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>64</v>
       </c>
       <c r="B89" t="s">
         <v>182</v>
       </c>
-      <c r="C89" t="s">
+      <c r="C89" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D89">
@@ -21522,14 +21528,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>65</v>
       </c>
       <c r="B90" t="s">
         <v>183</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C90" s="8" t="s">
         <v>65</v>
       </c>
       <c r="D90">
@@ -21537,14 +21543,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>184</v>
       </c>
       <c r="B91" t="s">
         <v>185</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C91" s="8" t="s">
         <v>184</v>
       </c>
       <c r="D91">
@@ -21552,14 +21558,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>186</v>
       </c>
       <c r="B92" t="s">
         <v>187</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C92" s="8" t="s">
         <v>186</v>
       </c>
       <c r="D92">
@@ -21567,14 +21573,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>188</v>
       </c>
       <c r="B93" t="s">
         <v>189</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C93" s="8" t="s">
         <v>188</v>
       </c>
       <c r="D93">
@@ -21582,14 +21588,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>66</v>
       </c>
       <c r="B94" t="s">
         <v>190</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C94" s="8" t="s">
         <v>66</v>
       </c>
       <c r="D94">
@@ -21597,14 +21603,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>71</v>
       </c>
       <c r="B95" t="s">
         <v>72</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C95" s="8" t="s">
         <v>71</v>
       </c>
       <c r="D95">
@@ -21612,14 +21618,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>68</v>
       </c>
       <c r="B96" t="s">
         <v>191</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C96" s="8" t="s">
         <v>68</v>
       </c>
       <c r="D96">
@@ -21627,14 +21633,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>67</v>
       </c>
       <c r="B97" t="s">
         <v>192</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C97" s="8" t="s">
         <v>67</v>
       </c>
       <c r="D97">
@@ -21651,11 +21657,11 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74D7E07A-B921-43B9-871A-3B92B3A0872A}">
   <dimension ref="A1:G47"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.5546875" customWidth="1"/>
-    <col min="2" max="2" width="39.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -22387,10 +22393,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{545EE0D3-A3EF-48C1-9D98-055E5CCFD75E}">
   <dimension ref="A1:D71"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -23468,11 +23474,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A02D50D-E7F1-4642-AB20-135908E70A20}">
   <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.5546875" customWidth="1"/>
-    <col min="2" max="2" width="39.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="0.5703125" customWidth="1"/>
+    <col min="2" max="2" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -24819,11 +24825,11 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A34EF7-3847-41CF-877F-358A14CEC3E4}">
   <dimension ref="A1:D75"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.6640625" customWidth="1"/>
-    <col min="2" max="2" width="45.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="45.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -25960,11 +25966,11 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D40B26C-3BFF-4A1D-BCAE-0DAF6FE91D49}">
   <dimension ref="A1:D103"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.6640625" customWidth="1"/>
-    <col min="2" max="2" width="47.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -27521,11 +27527,11 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{530D36B1-0236-481E-A2AF-2328F5B26377}">
   <dimension ref="A1:D93"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.5546875" customWidth="1"/>
-    <col min="2" max="2" width="43.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.5703125" customWidth="1"/>
+    <col min="2" max="2" width="43.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -28933,12 +28939,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{858D5447-E52A-42D1-A486-7CF77408D7C3}">
   <dimension ref="A1:J124"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" customWidth="1"/>
-    <col min="2" max="2" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="45.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="4" max="4" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -30514,9 +30520,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43811B03-43E2-4782-9D39-F9713A0F8753}">
   <dimension ref="A1:B87"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -31225,9 +31231,9 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D08DFAB1-9E61-4254-9811-1F3F956BD79E}">
   <dimension ref="A1:B60"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.109375" customWidth="1"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -31719,10 +31725,10 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09798D79-8D76-46CF-94E3-EC0065A655D6}">
   <dimension ref="A1:B97"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.44140625" customWidth="1"/>
+    <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -32510,11 +32516,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FECA4D5-D00E-4B19-AD07-C62E084089A5}">
   <dimension ref="A1:D54"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.33203125" customWidth="1"/>
-    <col min="2" max="2" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -33336,9 +33342,9 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F9C153A-34A1-4751-94A0-8A0AEB01D0EE}">
   <dimension ref="A1:B92"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -34086,9 +34092,9 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78FE89D1-1A38-47C0-BF48-67C0AFCF2A70}">
   <dimension ref="A1:B95"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -34861,9 +34867,9 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87E319DD-1851-42DE-BDA8-B72117C6F2E4}">
   <dimension ref="A1:B132"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -35931,9 +35937,9 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24D6E174-7436-4BBD-9FCA-42F950DFDE75}">
   <dimension ref="A1:B103"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -36769,9 +36775,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10038B29-C4CD-41F9-A15F-0E089CF74F75}">
   <dimension ref="A1:B96"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -37551,9 +37557,9 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9A0F5D8-CE40-425B-B93B-83EC06FA1104}">
   <dimension ref="A1:B108"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -38429,9 +38435,9 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54EBE5E2-80D0-4BB8-A544-C7F5CF55B910}">
   <dimension ref="A1:B135"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -39523,9 +39529,9 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98848FD4-CB05-4EEF-B530-7955D1D1F0FA}">
   <dimension ref="A1:B107"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -40394,9 +40400,9 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8837B5A-76D8-4E67-BC60-8580F3823942}">
   <dimension ref="A1:B59"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.77734375" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -40880,9 +40886,9 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6C5DD33-B8B7-446E-8652-826E854ECC53}">
   <dimension ref="A1:B86"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -41582,11 +41588,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C968D5F0-DE17-4F0F-B537-3641078E9596}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.77734375" customWidth="1"/>
-    <col min="2" max="2" width="40.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="40.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -42213,7 +42219,7 @@
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35902E0-5DA8-4F9A-A665-EE84FD306EF5}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -42223,10 +42229,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B62F886-2CFB-45CB-BDE0-2813C223E0D3}">
   <dimension ref="A1:D63"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.21875" customWidth="1"/>
-    <col min="2" max="2" width="39.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.28515625" customWidth="1"/>
+    <col min="2" max="2" width="39.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -43184,11 +43190,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7D71447-4409-44C6-A77A-F11D85C4FD8C}">
   <dimension ref="A1:D47"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.6640625" customWidth="1"/>
-    <col min="2" max="2" width="43.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -43905,11 +43911,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DF84DC-49AB-4C66-9301-8638E07CFDCC}">
   <dimension ref="A1:D55"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.6640625" customWidth="1"/>
-    <col min="2" max="2" width="47.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="0.7109375" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -44747,11 +44753,11 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CB692C9-E04B-4223-92B0-8223893898A1}">
   <dimension ref="A1:D82"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="0.44140625" customWidth="1"/>
-    <col min="2" max="2" width="39.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="1" max="1" width="0.42578125" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -45915,11 +45921,11 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCE5D55C-02F6-411E-8A17-AD1C379CA153}">
   <dimension ref="A1:F77"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -46981,10 +46987,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79858DFC-F1B9-400E-9CD6-8648C30EADE9}">
   <dimension ref="A1:B86"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
